--- a/PMS_Report_DPR-385_Period_ALL_to_2026-07-26.xlsx
+++ b/PMS_Report_DPR-385_Period_ALL_to_2026-07-26.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26 16:46</t>
+          <t>2026-07-26 17:02</t>
         </is>
       </c>
     </row>

--- a/PMS_Report_DPR-385_Period_ALL_to_2026-07-26.xlsx
+++ b/PMS_Report_DPR-385_Period_ALL_to_2026-07-26.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26 17:02</t>
+          <t>2026-07-26 17:34</t>
         </is>
       </c>
     </row>
